--- a/大陸シリーズ目次順番.xlsx
+++ b/大陸シリーズ目次順番.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\du34f\Downloads\TanoContSeries-TanoContBTAP4 (13)as\TanoContSeries-TanoContBTAP4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\du34f\Downloads\TanoContSeries-TanoContBTAP4 (22)\TanoContSeries-TanoContBTAP4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84602953-521F-4E82-B212-7AA2167F5642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D8243E-F090-495C-A9DD-8624EA87E30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{E96F2A6A-F138-4C1D-8914-69711554E5DA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E96F2A6A-F138-4C1D-8914-69711554E5DA}"/>
   </bookViews>
   <sheets>
     <sheet name="やりかたについて" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="107">
   <si>
     <t>Dictionary</t>
   </si>
@@ -528,6 +528,20 @@
     </rPh>
     <rPh sb="27" eb="29">
       <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tochino</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>災いの日</t>
+    <rPh sb="0" eb="1">
+      <t>ワザワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -933,7 +947,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8546C6-5C23-4432-926E-DD5F7D04EAE7}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
@@ -969,33 +983,33 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C3" t="b">
         <v>0</v>
@@ -1007,21 +1021,21 @@
         <v>94</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>93</v>
@@ -1030,64 +1044,64 @@
         <v>94</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -1099,7 +1113,7 @@
         <v>45</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7">
         <v>17</v>
@@ -1107,36 +1121,36 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
         <v>40</v>
@@ -1145,18 +1159,18 @@
         <v>42</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
@@ -1168,18 +1182,18 @@
         <v>42</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
@@ -1191,18 +1205,18 @@
         <v>42</v>
       </c>
       <c r="F11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
@@ -1214,21 +1228,21 @@
         <v>42</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="s">
         <v>40</v>
@@ -1237,18 +1251,18 @@
         <v>42</v>
       </c>
       <c r="F13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G13">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" t="b">
         <v>1</v>
@@ -1260,18 +1274,18 @@
         <v>42</v>
       </c>
       <c r="F14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="b">
         <v>1</v>
@@ -1283,18 +1297,18 @@
         <v>42</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>
@@ -1306,18 +1320,18 @@
         <v>42</v>
       </c>
       <c r="F16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="b">
         <v>1</v>
@@ -1329,18 +1343,18 @@
         <v>42</v>
       </c>
       <c r="F17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" t="b">
         <v>1</v>
@@ -1352,18 +1366,18 @@
         <v>42</v>
       </c>
       <c r="F18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G18">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C19" t="b">
         <v>1</v>
@@ -1375,41 +1389,41 @@
         <v>42</v>
       </c>
       <c r="F19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G19">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" t="b">
         <v>0</v>
@@ -1421,18 +1435,18 @@
         <v>44</v>
       </c>
       <c r="F21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C22" t="b">
         <v>0</v>
@@ -1444,21 +1458,21 @@
         <v>44</v>
       </c>
       <c r="F22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="s">
         <v>39</v>
@@ -1467,21 +1481,21 @@
         <v>44</v>
       </c>
       <c r="F23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G23">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="s">
         <v>39</v>
@@ -1490,21 +1504,21 @@
         <v>44</v>
       </c>
       <c r="F24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="s">
         <v>39</v>
@@ -1513,18 +1527,18 @@
         <v>44</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C26" t="b">
         <v>1</v>
@@ -1536,21 +1550,21 @@
         <v>44</v>
       </c>
       <c r="F26">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="s">
         <v>39</v>
@@ -1559,21 +1573,21 @@
         <v>44</v>
       </c>
       <c r="F27">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
@@ -1582,41 +1596,41 @@
         <v>44</v>
       </c>
       <c r="F28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C30" t="b">
         <v>0</v>
@@ -1628,21 +1642,21 @@
         <v>43</v>
       </c>
       <c r="F30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="s">
         <v>38</v>
@@ -1651,21 +1665,21 @@
         <v>43</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
@@ -1674,7 +1688,7 @@
         <v>43</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G32">
         <v>21</v>
@@ -1682,10 +1696,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
@@ -1697,18 +1711,18 @@
         <v>43</v>
       </c>
       <c r="F33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G33">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
@@ -1720,18 +1734,18 @@
         <v>43</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G34">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
@@ -1743,18 +1757,18 @@
         <v>43</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G35">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C36" t="b">
         <v>0</v>
@@ -1766,18 +1780,18 @@
         <v>43</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C37" t="b">
         <v>0</v>
@@ -1789,7 +1803,7 @@
         <v>43</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37">
         <v>19</v>
@@ -1797,10 +1811,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" t="b">
         <v>0</v>
@@ -1812,64 +1826,64 @@
         <v>43</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C39" t="b">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C40" t="b">
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E40" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C41" t="b">
         <v>0</v>
@@ -1889,10 +1903,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
@@ -1910,9 +1924,32 @@
         <v>0</v>
       </c>
     </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G38" xr:uid="{BE8546C6-5C23-4432-926E-DD5F7D04EAE7}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G41">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G43">
       <sortCondition descending="1" ref="F1:F38"/>
     </sortState>
   </autoFilter>
@@ -1946,41 +1983,41 @@
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A2 &amp; IF(Sheet1!C2, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Kazasaki2)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Tochino)'&gt;</v>
       </c>
       <c r="B2" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B2 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;第二章後編&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;災いの日&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C2" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A2 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Kazasaki2&lt;/td&gt;</v>
+        <v>&lt;td&gt;Tochino&lt;/td&gt;</v>
       </c>
       <c r="D2" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E2 &amp; "'&gt;" &amp; Sheet1!D2 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;div class='series_color_tag kazasaki'&gt;5.風咲&lt;/div&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;div class='series_color_tag variation'&gt;3.多様&lt;/div&gt;&lt;/td&gt;</v>
       </c>
       <c r="E2" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F2 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;38&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;39&lt;/td&gt;</v>
       </c>
       <c r="F2" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G2 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;2&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;10&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A3 &amp; IF(Sheet1!C3, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Kazasaki)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Kazasaki2)'&gt;</v>
       </c>
       <c r="B3" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B3 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;第二章前編&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;第二章後編&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C3" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A3 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Kazasaki&lt;/td&gt;</v>
+        <v>&lt;td&gt;Kazasaki2&lt;/td&gt;</v>
       </c>
       <c r="D3" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E3 &amp; "'&gt;" &amp; Sheet1!D3 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -1988,25 +2025,25 @@
       </c>
       <c r="E3" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F3 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;37&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;38&lt;/td&gt;</v>
       </c>
       <c r="F3" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G3 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;3&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;2&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A4 &amp; IF(Sheet1!C4, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Mitsuyoshi, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Kazasaki)'&gt;</v>
       </c>
       <c r="B4" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B4 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;第一章&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;第二章前編&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C4" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A4 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Mitsuyoshi&lt;/td&gt;</v>
+        <v>&lt;td&gt;Kazasaki&lt;/td&gt;</v>
       </c>
       <c r="D4" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E4 &amp; "'&gt;" &amp; Sheet1!D4 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2014,77 +2051,77 @@
       </c>
       <c r="E4" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F4 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;36&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;37&lt;/td&gt;</v>
       </c>
       <c r="F4" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G4 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;1&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;3&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A5 &amp; IF(Sheet1!C5, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Nitori, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Mitsuyoshi, true)'&gt;</v>
       </c>
       <c r="B5" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B5 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;二鳥からの手紙&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;第一章&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C5" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A5 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Nitori&lt;/td&gt;</v>
+        <v>&lt;td&gt;Mitsuyoshi&lt;/td&gt;</v>
       </c>
       <c r="D5" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E5 &amp; "'&gt;" &amp; Sheet1!D5 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;div class='series_color_tag minda2'&gt;2.ミンダ後編&lt;/div&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;div class='series_color_tag kazasaki'&gt;5.風咲&lt;/div&gt;&lt;/td&gt;</v>
       </c>
       <c r="E5" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F5 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;35&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;36&lt;/td&gt;</v>
       </c>
       <c r="F5" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G5 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;26&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;1&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A6 &amp; IF(Sheet1!C6, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(RNakia, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Nitori, true)'&gt;</v>
       </c>
       <c r="B6" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B6 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;伝説の復古&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;二鳥からの手紙&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C6" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A6 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;RNakia&lt;/td&gt;</v>
+        <v>&lt;td&gt;Nitori&lt;/td&gt;</v>
       </c>
       <c r="D6" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E6 &amp; "'&gt;" &amp; Sheet1!D6 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;div class='series_color_tag sana'&gt;4.サナ&lt;/div&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;div class='series_color_tag minda2'&gt;2.ミンダ後編&lt;/div&gt;&lt;/td&gt;</v>
       </c>
       <c r="E6" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F6 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;34&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;35&lt;/td&gt;</v>
       </c>
       <c r="F6" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G6 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;16&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;27&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A7 &amp; IF(Sheet1!C7, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Habaic, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(RNakia, true)'&gt;</v>
       </c>
       <c r="B7" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B7 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;流星の夜&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;伝説の復古&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C7" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A7 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Habaic&lt;/td&gt;</v>
+        <v>&lt;td&gt;RNakia&lt;/td&gt;</v>
       </c>
       <c r="D7" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E7 &amp; "'&gt;" &amp; Sheet1!D7 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2092,7 +2129,7 @@
       </c>
       <c r="E7" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F7 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;33&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;34&lt;/td&gt;</v>
       </c>
       <c r="F7" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G7 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
@@ -2102,41 +2139,41 @@
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A8 &amp; IF(Sheet1!C8, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Utagemaru, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Habaic, true)'&gt;</v>
       </c>
       <c r="B8" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B8 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;宴丸の使命&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;流星の夜&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C8" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A8 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Utagemaru&lt;/td&gt;</v>
+        <v>&lt;td&gt;Habaic&lt;/td&gt;</v>
       </c>
       <c r="D8" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E8 &amp; "'&gt;" &amp; Sheet1!D8 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;div class='series_color_tag variation'&gt;3.多様&lt;/div&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;div class='series_color_tag sana'&gt;4.サナ&lt;/div&gt;&lt;/td&gt;</v>
       </c>
       <c r="E8" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F8 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;32&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;33&lt;/td&gt;</v>
       </c>
       <c r="F8" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G8 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;8&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;18&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A9 &amp; IF(Sheet1!C9, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Meiju)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Utagemaru, true)'&gt;</v>
       </c>
       <c r="B9" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B9 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;空船なりの忠誠&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;宴丸の使命&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C9" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A9 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Meiju&lt;/td&gt;</v>
+        <v>&lt;td&gt;Utagemaru&lt;/td&gt;</v>
       </c>
       <c r="D9" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E9 &amp; "'&gt;" &amp; Sheet1!D9 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2144,25 +2181,25 @@
       </c>
       <c r="E9" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F9 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;31&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;32&lt;/td&gt;</v>
       </c>
       <c r="F9" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G9 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;4&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;8&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A10 &amp; IF(Sheet1!C10, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Seri)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Meiju)'&gt;</v>
       </c>
       <c r="B10" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B10 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;カッターの戦略&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;空船なりの忠誠&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C10" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A10 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Seri&lt;/td&gt;</v>
+        <v>&lt;td&gt;Meiju&lt;/td&gt;</v>
       </c>
       <c r="D10" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E10 &amp; "'&gt;" &amp; Sheet1!D10 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2170,25 +2207,25 @@
       </c>
       <c r="E10" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F10 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;30&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;31&lt;/td&gt;</v>
       </c>
       <c r="F10" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G10 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;7&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;4&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A11 &amp; IF(Sheet1!C11, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Uzinos)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Seri)'&gt;</v>
       </c>
       <c r="B11" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B11 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;永王の衝撃&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;カッターの戦略&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C11" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A11 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Uzinos&lt;/td&gt;</v>
+        <v>&lt;td&gt;Seri&lt;/td&gt;</v>
       </c>
       <c r="D11" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E11 &amp; "'&gt;" &amp; Sheet1!D11 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2196,25 +2233,25 @@
       </c>
       <c r="E11" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F11 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;29&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;30&lt;/td&gt;</v>
       </c>
       <c r="F11" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G11 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;6&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;7&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A12 &amp; IF(Sheet1!C12, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Goeibara)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Uzinos)'&gt;</v>
       </c>
       <c r="B12" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B12 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;永王への帰依&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;永王の衝撃&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C12" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A12 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Goeibara&lt;/td&gt;</v>
+        <v>&lt;td&gt;Uzinos&lt;/td&gt;</v>
       </c>
       <c r="D12" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E12 &amp; "'&gt;" &amp; Sheet1!D12 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2222,25 +2259,25 @@
       </c>
       <c r="E12" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F12 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;28&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;29&lt;/td&gt;</v>
       </c>
       <c r="F12" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G12 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;37&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;6&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A13 &amp; IF(Sheet1!C13, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Gerufaru, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Goeibara)'&gt;</v>
       </c>
       <c r="B13" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B13 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ゲルファルの身の上&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;永王への帰依&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C13" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A13 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Gerufaru&lt;/td&gt;</v>
+        <v>&lt;td&gt;Goeibara&lt;/td&gt;</v>
       </c>
       <c r="D13" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E13 &amp; "'&gt;" &amp; Sheet1!D13 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2248,25 +2285,25 @@
       </c>
       <c r="E13" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F13 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;27&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;28&lt;/td&gt;</v>
       </c>
       <c r="F13" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G13 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;34&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;38&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A14 &amp; IF(Sheet1!C14, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Gebu, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Gerufaru, true)'&gt;</v>
       </c>
       <c r="B14" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B14 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;迷い子ゲブ&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ゲルファルの身の上&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C14" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A14 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Gebu&lt;/td&gt;</v>
+        <v>&lt;td&gt;Gerufaru&lt;/td&gt;</v>
       </c>
       <c r="D14" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E14 &amp; "'&gt;" &amp; Sheet1!D14 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2274,25 +2311,25 @@
       </c>
       <c r="E14" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F14 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;26&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;27&lt;/td&gt;</v>
       </c>
       <c r="F14" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G14 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;5&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;35&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A15 &amp; IF(Sheet1!C15, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Paripero, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Gebu, true)'&gt;</v>
       </c>
       <c r="B15" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B15 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;禁忌知見集&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;迷い子ゲブ&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C15" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A15 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Paripero&lt;/td&gt;</v>
+        <v>&lt;td&gt;Gebu&lt;/td&gt;</v>
       </c>
       <c r="D15" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E15 &amp; "'&gt;" &amp; Sheet1!D15 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2300,25 +2337,25 @@
       </c>
       <c r="E15" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F15 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;25&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;26&lt;/td&gt;</v>
       </c>
       <c r="F15" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G15 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;15&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;5&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A16 &amp; IF(Sheet1!C16, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Akisato, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Paripero, true)'&gt;</v>
       </c>
       <c r="B16" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B16 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ばせる様の進軍&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;禁忌知見集&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C16" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A16 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Akisato&lt;/td&gt;</v>
+        <v>&lt;td&gt;Paripero&lt;/td&gt;</v>
       </c>
       <c r="D16" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E16 &amp; "'&gt;" &amp; Sheet1!D16 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2326,25 +2363,25 @@
       </c>
       <c r="E16" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F16 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;24&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;25&lt;/td&gt;</v>
       </c>
       <c r="F16" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G16 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;12&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;16&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A17 &amp; IF(Sheet1!C17, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Baseru, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Akisato, true)'&gt;</v>
       </c>
       <c r="B17" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B17 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;あらわれるばせる様&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ばせる様の進軍&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C17" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A17 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Baseru&lt;/td&gt;</v>
+        <v>&lt;td&gt;Akisato&lt;/td&gt;</v>
       </c>
       <c r="D17" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E17 &amp; "'&gt;" &amp; Sheet1!D17 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2352,25 +2389,25 @@
       </c>
       <c r="E17" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F17 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;23&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;24&lt;/td&gt;</v>
       </c>
       <c r="F17" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G17 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;11&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;13&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A18 &amp; IF(Sheet1!C18, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Yoshine2, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Baseru, true)'&gt;</v>
       </c>
       <c r="B18" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B18 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ばせる様の暴動と芦音&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;あらわれるばせる様&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C18" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A18 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Yoshine2&lt;/td&gt;</v>
+        <v>&lt;td&gt;Baseru&lt;/td&gt;</v>
       </c>
       <c r="D18" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E18 &amp; "'&gt;" &amp; Sheet1!D18 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2378,25 +2415,25 @@
       </c>
       <c r="E18" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F18 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;22&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;23&lt;/td&gt;</v>
       </c>
       <c r="F18" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G18 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;14&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;12&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A19 &amp; IF(Sheet1!C19, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Umiao, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Yoshine2, true)'&gt;</v>
       </c>
       <c r="B19" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B19 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;緑ヶ淵の閉山&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ばせる様の暴動と芦音&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C19" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A19 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Umiao&lt;/td&gt;</v>
+        <v>&lt;td&gt;Yoshine2&lt;/td&gt;</v>
       </c>
       <c r="D19" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E19 &amp; "'&gt;" &amp; Sheet1!D19 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2404,51 +2441,51 @@
       </c>
       <c r="E19" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F19 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;21&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;22&lt;/td&gt;</v>
       </c>
       <c r="F19" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G19 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;13&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;15&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A20 &amp; IF(Sheet1!C20, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Minda5_2)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Umiao, true)'&gt;</v>
       </c>
       <c r="B20" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B20 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;おわり、その先へ2&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;緑ヶ淵の閉山&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C20" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A20 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Minda5_2&lt;/td&gt;</v>
+        <v>&lt;td&gt;Umiao&lt;/td&gt;</v>
       </c>
       <c r="D20" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E20 &amp; "'&gt;" &amp; Sheet1!D20 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;div class='series_color_tag minda2'&gt;2.ミンダ後編&lt;/div&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;div class='series_color_tag variation'&gt;3.多様&lt;/div&gt;&lt;/td&gt;</v>
       </c>
       <c r="E20" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F20 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;20&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;21&lt;/td&gt;</v>
       </c>
       <c r="F20" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G20 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;36&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;14&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A21 &amp; IF(Sheet1!C21, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Minda5_1)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Minda5_2)'&gt;</v>
       </c>
       <c r="B21" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B21 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;おわり、その先へ1&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;おわり、その先へ2&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C21" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A21 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Minda5_1&lt;/td&gt;</v>
+        <v>&lt;td&gt;Minda5_2&lt;/td&gt;</v>
       </c>
       <c r="D21" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E21 &amp; "'&gt;" &amp; Sheet1!D21 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2456,25 +2493,25 @@
       </c>
       <c r="E21" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F21 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;19&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;20&lt;/td&gt;</v>
       </c>
       <c r="F21" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G21 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;35&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;37&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A22 &amp; IF(Sheet1!C22, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Minda4)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Minda5_1)'&gt;</v>
       </c>
       <c r="B22" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B22 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;光の足音と背後&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;おわり、その先へ1&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C22" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A22 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Minda4&lt;/td&gt;</v>
+        <v>&lt;td&gt;Minda5_1&lt;/td&gt;</v>
       </c>
       <c r="D22" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E22 &amp; "'&gt;" &amp; Sheet1!D22 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2482,25 +2519,25 @@
       </c>
       <c r="E22" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F22 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;18&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;19&lt;/td&gt;</v>
       </c>
       <c r="F22" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G22 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;33&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;36&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A23 &amp; IF(Sheet1!C23, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Hitami2, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Minda4)'&gt;</v>
       </c>
       <c r="B23" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B23 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;煙石様の再来&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;光の足音と背後&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C23" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A23 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Hitami2&lt;/td&gt;</v>
+        <v>&lt;td&gt;Minda4&lt;/td&gt;</v>
       </c>
       <c r="D23" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E23 &amp; "'&gt;" &amp; Sheet1!D23 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2508,25 +2545,25 @@
       </c>
       <c r="E23" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F23 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;17&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;18&lt;/td&gt;</v>
       </c>
       <c r="F23" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G23 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;30&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;34&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A24 &amp; IF(Sheet1!C24, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Kurokasa)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Hitami2, true)'&gt;</v>
       </c>
       <c r="B24" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B24 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;大鹿が呼ぶ&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;煙石様の再来&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C24" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A24 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Kurokasa&lt;/td&gt;</v>
+        <v>&lt;td&gt;Hitami2&lt;/td&gt;</v>
       </c>
       <c r="D24" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E24 &amp; "'&gt;" &amp; Sheet1!D24 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2534,25 +2571,25 @@
       </c>
       <c r="E24" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F24 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;16&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;17&lt;/td&gt;</v>
       </c>
       <c r="F24" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G24 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;32&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;31&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A25 &amp; IF(Sheet1!C25, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Inome3, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Kurokasa)'&gt;</v>
       </c>
       <c r="B25" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B25 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;猪目の失態と動揺&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;大鹿が呼ぶ&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C25" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A25 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Inome3&lt;/td&gt;</v>
+        <v>&lt;td&gt;Kurokasa&lt;/td&gt;</v>
       </c>
       <c r="D25" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E25 &amp; "'&gt;" &amp; Sheet1!D25 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2560,25 +2597,25 @@
       </c>
       <c r="E25" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F25 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;15&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;16&lt;/td&gt;</v>
       </c>
       <c r="F25" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G25 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;25&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;33&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A26 &amp; IF(Sheet1!C26, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Minda3, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Inome3, true)'&gt;</v>
       </c>
       <c r="B26" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B26 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ミンダの夢と黒傘の不安&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;猪目の失態と動揺&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C26" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A26 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Minda3&lt;/td&gt;</v>
+        <v>&lt;td&gt;Inome3&lt;/td&gt;</v>
       </c>
       <c r="D26" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E26 &amp; "'&gt;" &amp; Sheet1!D26 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2586,25 +2623,25 @@
       </c>
       <c r="E26" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F26 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;14&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;15&lt;/td&gt;</v>
       </c>
       <c r="F26" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G26 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;24&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;26&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A27 &amp; IF(Sheet1!C27, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Inome2)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Minda3, true)'&gt;</v>
       </c>
       <c r="B27" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B27 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;揺れ動く猪目&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ミンダの夢と黒傘の不安&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C27" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A27 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Inome2&lt;/td&gt;</v>
+        <v>&lt;td&gt;Minda3&lt;/td&gt;</v>
       </c>
       <c r="D27" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E27 &amp; "'&gt;" &amp; Sheet1!D27 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2612,25 +2649,25 @@
       </c>
       <c r="E27" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F27 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;13&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;14&lt;/td&gt;</v>
       </c>
       <c r="F27" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G27 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;9&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;25&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A28 &amp; IF(Sheet1!C28, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Hitami, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Inome2)'&gt;</v>
       </c>
       <c r="B28" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B28 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ひたみの苦悩&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;揺れ動く猪目&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C28" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A28 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Hitami&lt;/td&gt;</v>
+        <v>&lt;td&gt;Inome2&lt;/td&gt;</v>
       </c>
       <c r="D28" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E28 &amp; "'&gt;" &amp; Sheet1!D28 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2638,51 +2675,51 @@
       </c>
       <c r="E28" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F28 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;12&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;13&lt;/td&gt;</v>
       </c>
       <c r="F28" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G28 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;27&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;9&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A29 &amp; IF(Sheet1!C29, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Yoshine)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Hitami, true)'&gt;</v>
       </c>
       <c r="B29" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B29 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;爆薬運搬任務&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ひたみの苦悩&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C29" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A29 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Yoshine&lt;/td&gt;</v>
+        <v>&lt;td&gt;Hitami&lt;/td&gt;</v>
       </c>
       <c r="D29" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E29 &amp; "'&gt;" &amp; Sheet1!D29 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;div class='series_color_tag minda1'&gt;1.ミンダ前編&lt;/div&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;div class='series_color_tag minda2'&gt;2.ミンダ後編&lt;/div&gt;&lt;/td&gt;</v>
       </c>
       <c r="E29" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F29 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;11&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;12&lt;/td&gt;</v>
       </c>
       <c r="F29" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G29 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;29&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;28&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A30 &amp; IF(Sheet1!C30, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Ippu)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Yoshine)'&gt;</v>
       </c>
       <c r="B30" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B30 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;大鉱機の計画&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;爆薬運搬任務&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C30" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A30 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Ippu&lt;/td&gt;</v>
+        <v>&lt;td&gt;Yoshine&lt;/td&gt;</v>
       </c>
       <c r="D30" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E30 &amp; "'&gt;" &amp; Sheet1!D30 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2690,25 +2727,25 @@
       </c>
       <c r="E30" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F30 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;10&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;11&lt;/td&gt;</v>
       </c>
       <c r="F30" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G30 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;28&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;30&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A31 &amp; IF(Sheet1!C31, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Suihoun, true)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Ippu)'&gt;</v>
       </c>
       <c r="B31" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B31 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;乾いた大地、氷の大地&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;大鉱機の計画&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C31" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A31 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Suihoun&lt;/td&gt;</v>
+        <v>&lt;td&gt;Ippu&lt;/td&gt;</v>
       </c>
       <c r="D31" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E31 &amp; "'&gt;" &amp; Sheet1!D31 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2716,25 +2753,25 @@
       </c>
       <c r="E31" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F31 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;9&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;10&lt;/td&gt;</v>
       </c>
       <c r="F31" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G31 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;20&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;29&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A32 &amp; IF(Sheet1!C32, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Fumi)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Suihoun, true)'&gt;</v>
       </c>
       <c r="B32" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B32 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;五黒家と根の教会&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;乾いた大地、氷の大地&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C32" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A32 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Fumi&lt;/td&gt;</v>
+        <v>&lt;td&gt;Suihoun&lt;/td&gt;</v>
       </c>
       <c r="D32" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E32 &amp; "'&gt;" &amp; Sheet1!D32 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2742,7 +2779,7 @@
       </c>
       <c r="E32" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F32 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;8&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;9&lt;/td&gt;</v>
       </c>
       <c r="F32" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G32 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
@@ -2752,15 +2789,15 @@
     <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A33 &amp; IF(Sheet1!C33, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Baruru)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Fumi)'&gt;</v>
       </c>
       <c r="B33" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B33 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;バルルとニシン&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;五黒家と根の教会&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C33" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A33 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Baruru&lt;/td&gt;</v>
+        <v>&lt;td&gt;Fumi&lt;/td&gt;</v>
       </c>
       <c r="D33" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E33 &amp; "'&gt;" &amp; Sheet1!D33 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2768,25 +2805,25 @@
       </c>
       <c r="E33" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F33 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;7&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;8&lt;/td&gt;</v>
       </c>
       <c r="F33" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G33 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;31&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;22&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A34 &amp; IF(Sheet1!C34, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Sachi)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Baruru)'&gt;</v>
       </c>
       <c r="B34" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B34 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;白霧鉄山にて&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;バルルとニシン&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C34" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A34 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Sachi&lt;/td&gt;</v>
+        <v>&lt;td&gt;Baruru&lt;/td&gt;</v>
       </c>
       <c r="D34" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E34 &amp; "'&gt;" &amp; Sheet1!D34 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2794,25 +2831,25 @@
       </c>
       <c r="E34" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F34 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;6&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;7&lt;/td&gt;</v>
       </c>
       <c r="F34" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G34 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;23&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;32&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A35 &amp; IF(Sheet1!C35, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Sakuma)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Sachi)'&gt;</v>
       </c>
       <c r="B35" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B35 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;池家さくまの雑務&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;白霧鉄山にて&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C35" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A35 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Sakuma&lt;/td&gt;</v>
+        <v>&lt;td&gt;Sachi&lt;/td&gt;</v>
       </c>
       <c r="D35" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E35 &amp; "'&gt;" &amp; Sheet1!D35 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2820,25 +2857,25 @@
       </c>
       <c r="E35" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F35 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;5&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;6&lt;/td&gt;</v>
       </c>
       <c r="F35" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G35 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;22&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;24&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A36 &amp; IF(Sheet1!C36, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Inome)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Sakuma)'&gt;</v>
       </c>
       <c r="B36" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B36 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;猪目 遥音の出張&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;池家さくまの雑務&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C36" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A36 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Inome&lt;/td&gt;</v>
+        <v>&lt;td&gt;Sakuma&lt;/td&gt;</v>
       </c>
       <c r="D36" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E36 &amp; "'&gt;" &amp; Sheet1!D36 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2846,25 +2883,25 @@
       </c>
       <c r="E36" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F36 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;4&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;5&lt;/td&gt;</v>
       </c>
       <c r="F36" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G36 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;18&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;23&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A37 &amp; IF(Sheet1!C37, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Minda2)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Inome)'&gt;</v>
       </c>
       <c r="B37" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B37 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ミンダと赤い魚&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;猪目 遥音の出張&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C37" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A37 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Minda2&lt;/td&gt;</v>
+        <v>&lt;td&gt;Inome&lt;/td&gt;</v>
       </c>
       <c r="D37" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E37 &amp; "'&gt;" &amp; Sheet1!D37 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2872,7 +2909,7 @@
       </c>
       <c r="E37" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F37 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;3&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;4&lt;/td&gt;</v>
       </c>
       <c r="F37" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G37 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
@@ -2882,15 +2919,15 @@
     <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A38 &amp; IF(Sheet1!C38, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Minda)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Minda2)'&gt;</v>
       </c>
       <c r="B38" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B38 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;黒縄のミンダ&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;ミンダと赤い魚&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C38" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A38 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Minda&lt;/td&gt;</v>
+        <v>&lt;td&gt;Minda2&lt;/td&gt;</v>
       </c>
       <c r="D38" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E38 &amp; "'&gt;" &amp; Sheet1!D38 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2898,77 +2935,77 @@
       </c>
       <c r="E38" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F38 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;2&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;3&lt;/td&gt;</v>
       </c>
       <c r="F38" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G38 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;10&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;20&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A39 &amp; IF(Sheet1!C39, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Kunugi)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Minda)'&gt;</v>
       </c>
       <c r="B39" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B39 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;櫟木の一日&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;黒縄のミンダ&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C39" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A39 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Kunugi&lt;/td&gt;</v>
+        <v>&lt;td&gt;Minda&lt;/td&gt;</v>
       </c>
       <c r="D39" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E39 &amp; "'&gt;" &amp; Sheet1!D39 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;div class='series_color_tag variation'&gt;3.多様&lt;/div&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;div class='series_color_tag minda1'&gt;1.ミンダ前編&lt;/div&gt;&lt;/td&gt;</v>
       </c>
       <c r="E39" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F39 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;1&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;2&lt;/td&gt;</v>
       </c>
       <c r="F39" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G39 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;38&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;11&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A40 &amp; IF(Sheet1!C40, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Abstract)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Kunugi)'&gt;</v>
       </c>
       <c r="B40" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B40 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;あらすじ&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;櫟木の一日&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C40" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A40 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Abstract&lt;/td&gt;</v>
+        <v>&lt;td&gt;Kunugi&lt;/td&gt;</v>
       </c>
       <c r="D40" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E40 &amp; "'&gt;" &amp; Sheet1!D40 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;div class='series_color_tag meta'&gt;0.メタ&lt;/div&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;div class='series_color_tag variation'&gt;3.多様&lt;/div&gt;&lt;/td&gt;</v>
       </c>
       <c r="E40" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F40 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;0&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;1&lt;/td&gt;</v>
       </c>
       <c r="F40" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G40 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;0&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;39&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A41 &amp; IF(Sheet1!C41, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(Dictionary)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Abstract)'&gt;</v>
       </c>
       <c r="B41" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B41 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;辞書&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;あらすじ&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C41" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A41 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;Dictionary&lt;/td&gt;</v>
+        <v>&lt;td&gt;Abstract&lt;/td&gt;</v>
       </c>
       <c r="D41" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E41 &amp; "'&gt;" &amp; Sheet1!D41 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -2986,15 +3023,15 @@
     <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A42 &amp; IF(Sheet1!C42, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data(UserTour)'&gt;</v>
+        <v>&lt;tr onclick='load_data(Dictionary)'&gt;</v>
       </c>
       <c r="B42" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B42 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;画面説明&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;辞書&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C42" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A42 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;UserTour&lt;/td&gt;</v>
+        <v>&lt;td&gt;Dictionary&lt;/td&gt;</v>
       </c>
       <c r="D42" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E42 &amp; "'&gt;" &amp; Sheet1!D42 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
@@ -3012,27 +3049,27 @@
     <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" t="str">
         <f>"&lt;tr onclick='load_data(" &amp; Sheet1!A43 &amp; IF(Sheet1!C43, ", true", "") &amp;")'&gt;"</f>
-        <v>&lt;tr onclick='load_data()'&gt;</v>
+        <v>&lt;tr onclick='load_data(UserTour)'&gt;</v>
       </c>
       <c r="B43" t="str">
         <f>"&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;" &amp; Sheet1!B43 &amp; "&lt;/a&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;&lt;/a&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;a href='#' class='a_without_underline'&gt;画面説明&lt;/a&gt;&lt;/td&gt;</v>
       </c>
       <c r="C43" t="str">
         <f>"&lt;td&gt;" &amp; Sheet1!A43 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;UserTour&lt;/td&gt;</v>
       </c>
       <c r="D43" t="str">
         <f>"&lt;td&gt;&lt;div class='series_color_tag " &amp; Sheet1!E43 &amp; "'&gt;" &amp; Sheet1!D43 &amp; "&lt;/div&gt;&lt;/td&gt;"</f>
-        <v>&lt;td&gt;&lt;div class='series_color_tag '&gt;&lt;/div&gt;&lt;/td&gt;</v>
+        <v>&lt;td&gt;&lt;div class='series_color_tag meta'&gt;0.メタ&lt;/div&gt;&lt;/td&gt;</v>
       </c>
       <c r="E43" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!F43 &amp; "&lt;/td&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;&lt;/td&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;0&lt;/td&gt;</v>
       </c>
       <c r="F43" t="str">
         <f>"&lt;td class='hidden_th'&gt;" &amp; Sheet1!G43 &amp; "&lt;/td&gt;&lt;/tr&gt;"</f>
-        <v>&lt;td class='hidden_th'&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+        <v>&lt;td class='hidden_th'&gt;0&lt;/td&gt;&lt;/tr&gt;</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.45">
